--- a/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
@@ -38,8 +38,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCE5FF"/>
+        <bgColor rgb="00CCE5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -50,8 +62,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-        <bgColor rgb="00D9D2E9"/>
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,26 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CCE5FF"/>
-        <bgColor rgb="00CCE5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
+        <fgColor rgb="00D9D2E9"/>
+        <bgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>254129</v>
+        <v>250891</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -549,26 +549,24 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>08-09-2025 07:32:00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>254385</v>
+        <v>252216</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -577,26 +575,24 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:16:30</t>
+          <t>08-09-2025 08:49:29</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:48:30</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>08-09-2025 09:14:29</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>254713</v>
+        <v>253527</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -605,26 +601,24 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 14:40:35</t>
+          <t>08-09-2025 11:36:18</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 07:12:35</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>08-09-2025 12:05:18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>243569</v>
+        <v>253524</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -633,24 +627,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 08:02:33</t>
+          <t>08-09-2025 13:12:47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:33</t>
+          <t>08-09-2025 13:27:47</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>254156</v>
+        <v>253528</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -659,26 +653,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 08:41:13</t>
+          <t>08-09-2025 14:26:32</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>08-09-2025 14:41:32</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>254375</v>
+        <v>244023</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -687,24 +679,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:42</t>
+          <t>09-09-2025 08:40:43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 11:01:42</t>
+          <t>09-09-2025 09:01:43</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>254256</v>
+        <v>252939</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -713,24 +705,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 11:46:59</t>
+          <t>09-09-2025 09:10:01</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 12:03:59</t>
+          <t>09-09-2025 09:31:01</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>254519</v>
+        <v>252815</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -739,12 +731,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 12:54:55</t>
+          <t>09-09-2025 11:00:49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 13:09:55</t>
+          <t>09-09-2025 11:40:49</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -755,166 +747,164 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>254237</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:27:04</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:50:04</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
+      <c r="A10" s="3" t="n">
+        <v>253072</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:46:00</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>255039</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:54:10</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:17:10</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>7</v>
+      <c r="A11" s="3" t="n">
+        <v>253271</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 08:15:08</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 08:40:08</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>254824</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:26:19</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:58:19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>7</v>
+      <c r="A12" s="3" t="n">
+        <v>253278</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 09:22:46</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 09:47:46</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>254599</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:26:32</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:00:32</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>4</v>
+      <c r="A13" s="3" t="n">
+        <v>253317</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 10:16:11</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:02:11</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>253961</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:45:26</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:00:26</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4</v>
+      <c r="A14" s="3" t="n">
+        <v>253318</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 12:44:58</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 13:09:58</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>250284</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:36:21</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:59:21</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n">
+      <c r="A15" s="3" t="n">
+        <v>253260</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 14:01:31</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>08-09-2025 14:43:31</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>254165</v>
+        <v>253455</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -923,26 +913,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>09-09-2025 08:32:55</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>09-09-2025 08:57:55</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>254117</v>
+        <v>253247</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -951,24 +939,24 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>09-09-2025 09:53:29</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 09:07:19</t>
+          <t>09-09-2025 10:18:29</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>254107</v>
+        <v>253249</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -977,24 +965,24 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 09:16:29</t>
+          <t>09-09-2025 12:08:03</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 09:58:29</t>
+          <t>09-09-2025 12:50:03</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>254293</v>
+        <v>253706</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -1003,12 +991,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 12:53:32</t>
+          <t>09-09-2025 13:47:49</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 13:22:32</t>
+          <t>09-09-2025 14:22:49</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
@@ -1019,86 +1007,92 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>253838</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:41:23</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:08:23</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
+      <c r="A20" s="4" t="n">
+        <v>252702</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>05-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>05-09-2025 07:34:00</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>253362</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>05-09-2025 08:32:23</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>05-09-2025 08:47:23</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>252681</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>05-09-2025 09:45:46</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>05-09-2025 10:19:46</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>254605</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:56:45</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 08:29:45</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>254758</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:08:47</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:35:47</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>254556</v>
+        <v>253591</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
@@ -1107,12 +1101,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>05-09-2025 12:14:47</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>05-09-2025 12:29:47</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1121,12 +1115,12 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>254230</v>
+        <v>243569</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
@@ -1135,12 +1129,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>05-09-2025 12:47:12</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:25</t>
+          <t>05-09-2025 13:06:12</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -1152,7 +1146,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>254433</v>
+        <v>250284</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
@@ -1161,24 +1155,24 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 11:54:53</t>
+          <t>05-09-2025 13:27:52</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:53</t>
+          <t>05-09-2025 14:07:52</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>254106</v>
+        <v>252906</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
@@ -1187,24 +1181,24 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 13:17:44</t>
+          <t>08-09-2025 08:34:13</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 13:36:44</t>
+          <t>08-09-2025 09:12:13</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>254460</v>
+        <v>253140</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
@@ -1213,12 +1207,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:24:23</t>
+          <t>08-09-2025 09:46:57</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:23</t>
+          <t>08-09-2025 10:03:57</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -1230,7 +1224,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>254198</v>
+        <v>253100</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
@@ -1239,24 +1233,24 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:04</t>
+          <t>08-09-2025 10:59:47</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:04</t>
+          <t>08-09-2025 11:31:47</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>253885</v>
+        <v>253246</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
@@ -1265,24 +1259,24 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 12:41:04</t>
+          <t>08-09-2025 12:19:08</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 13:13:04</t>
+          <t>08-09-2025 12:34:08</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>254451</v>
+        <v>253372</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
@@ -1291,12 +1285,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 14:59:00</t>
+          <t>09-09-2025 07:48:23</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 07:18:00</t>
+          <t>09-09-2025 08:07:23</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -1307,90 +1301,86 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>254481</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>13-11-2025 12:00:00</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>13-11-2025 12:32:30</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n">
+      <c r="A31" s="4" t="n">
+        <v>253370</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 09:51:09</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 10:06:09</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>254762</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>13-11-2025 13:53:40</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>13-11-2025 14:28:10</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>2</v>
+      <c r="A32" s="4" t="n">
+        <v>253095</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 13:33:42</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 13:50:42</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>253865</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:01</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:34:31</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>2</v>
+      <c r="A33" s="4" t="n">
+        <v>253332</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>10-09-2025 07:07:01</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>10-09-2025 07:24:01</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>254245</v>
+        <v>252833</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -1399,12 +1389,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:17</t>
+          <t>09-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 10:03:47</t>
+          <t>09-09-2025 07:34:30</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
@@ -1416,7 +1406,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>254356</v>
+        <v>253223</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -1425,24 +1415,24 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:35</t>
+          <t>09-09-2025 08:49:17</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 12:04:05</t>
+          <t>09-09-2025 09:39:47</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>254381</v>
+        <v>252601</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -1451,12 +1441,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:41</t>
+          <t>09-09-2025 09:56:11</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 07:36:11</t>
+          <t>09-09-2025 10:28:41</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -1468,7 +1458,7 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>254652</v>
+        <v>253208</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -1477,12 +1467,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 09:00:03</t>
+          <t>09-09-2025 11:19:53</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 09:32:33</t>
+          <t>09-09-2025 11:52:23</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
@@ -1494,7 +1484,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>254756</v>
+        <v>253210</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -1503,52 +1493,50 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 10:01:17</t>
+          <t>09-09-2025 13:36:39</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 10:41:47</t>
+          <t>09-09-2025 14:07:09</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n">
-        <v>253694</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>13-11-2025 12:00:00</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>13-11-2025 12:45:00</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>2</v>
+      <c r="A39" s="5" t="n">
+        <v>252883</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>10-09-2025 07:41:18</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>10-09-2025 08:13:48</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>253380</v>
+        <v>252002</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
@@ -1557,12 +1545,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>04-09-2025 12:00:00</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:45</t>
+          <t>04-09-2025 12:55:00</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1571,12 +1559,12 @@
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>254598</v>
+        <v>253314</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
@@ -1585,24 +1573,26 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:02</t>
+          <t>04-09-2025 13:50:40</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:02</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>0</v>
+          <t>04-09-2025 14:40:40</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>252061</v>
+        <v>252569</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
@@ -1611,26 +1601,24 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:17</t>
+          <t>05-09-2025 07:24:05</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 13:05:17</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>05-09-2025 07:54:05</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>254546</v>
+        <v>252685</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
@@ -1639,24 +1627,26 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 13:41:27</t>
+          <t>05-09-2025 08:03:40</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 14:11:27</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>0</v>
+          <t>05-09-2025 08:33:40</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>235572</v>
+        <v>252682</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
@@ -1665,16 +1655,18 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:52</t>
+          <t>05-09-2025 09:48:14</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 08:30:52</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>0</v>
+          <t>05-09-2025 10:28:14</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F44" s="6" t="n">
         <v>4</v>
@@ -1682,7 +1674,7 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>254188</v>
+        <v>252582</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
@@ -1691,16 +1683,18 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 09:53:51</t>
+          <t>05-09-2025 11:51:38</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 10:23:51</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>0</v>
+          <t>05-09-2025 12:21:38</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F45" s="6" t="n">
         <v>1</v>
@@ -1708,7 +1702,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>254457</v>
+        <v>235572</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
@@ -1717,24 +1711,24 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 11:01:17</t>
+          <t>05-09-2025 13:07:43</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 11:26:17</t>
+          <t>05-09-2025 13:52:43</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>254437</v>
+        <v>253374</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
@@ -1743,12 +1737,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 11:30:13</t>
+          <t>08-09-2025 07:15:42</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 11:55:13</t>
+          <t>08-09-2025 07:45:42</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -1759,168 +1753,164 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>254941</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:32:00</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
+      <c r="A48" s="6" t="n">
+        <v>253036</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 08:45:19</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 09:25:19</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>253897</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:07:30</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:51:30</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>1</v>
+      <c r="A49" s="6" t="n">
+        <v>253710</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 10:44:03</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:29:03</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>254675</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:25:31</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:56:31</t>
-        </is>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
+      <c r="A50" s="6" t="n">
+        <v>253687</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:30:40</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 12:05:40</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>254512</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:30:28</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:47:28</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>1</v>
+      <c r="A51" s="6" t="n">
+        <v>253267</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 12:49:54</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>08-09-2025 13:19:54</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>253382</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:47:02</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:04:02</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>2</v>
+      <c r="A52" s="6" t="n">
+        <v>253268</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:04:16</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:29:16</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>254910</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 08:29:08</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 08:46:08</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>7</v>
+      <c r="A53" s="6" t="n">
+        <v>253359</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>09-09-2025 09:47:49</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>09-09-2025 10:17:49</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>254283</v>
+        <v>252827</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
@@ -1929,24 +1919,24 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 09:59:40</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 10:16:40</t>
+          <t>08-09-2025 07:17:00</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
-        <v>254555</v>
+        <v>253409</v>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
@@ -1955,24 +1945,24 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 11:52:26</t>
+          <t>08-09-2025 14:07:00</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:26</t>
+          <t>08-09-2025 14:24:00</t>
         </is>
       </c>
       <c r="E55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
-        <v>253650</v>
+        <v>253194</v>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
@@ -1981,24 +1971,24 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>18-11-2025 07:02:25</t>
+          <t>08-09-2025 14:51:11</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>18-11-2025 07:19:25</t>
+          <t>09-09-2025 07:06:11</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
-        <v>254309</v>
+        <v>252843</v>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
@@ -2007,364 +1997,370 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>18-11-2025 11:52:33</t>
+          <t>09-09-2025 10:25:16</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>18-11-2025 12:24:33</t>
+          <t>09-09-2025 10:52:16</t>
         </is>
       </c>
       <c r="E57" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>254714</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="A58" s="7" t="n">
+        <v>253425</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>09-09-2025 11:11:28</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>09-09-2025 11:34:28</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>253313</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>09-09-2025 14:00:49</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>09-09-2025 14:17:49</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>252995</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>10-09-2025 07:57:49</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>10-09-2025 08:14:49</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>253284</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:23:08</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:40:08</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>253602</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>10-09-2025 10:37:08</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>10-09-2025 10:54:08</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>253721</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:50:00</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 07:40:00</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>253686</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:19:23</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:54:23</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>253659</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 09:38:37</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>09-09-2025 10:03:37</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>253016</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 07:30:00</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F66" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>244023</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:21:28</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:56:28</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>254429</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:04:47</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:34:47</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>254291</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:35:01</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:05:01</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="n">
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>253259</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 08:43:23</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 09:18:23</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>254276</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:23:52</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:58:52</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>252679</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 10:27:37</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 11:12:37</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>254893</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 08:35:54</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:05:54</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>254189</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:52:35</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:22:35</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>255043</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:18:27</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:43:27</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>254521</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:47:44</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:17:44</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="n">
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>252664</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 12:12:37</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>05-09-2025 12:57:37</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>252811</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:57:25</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:32:25</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>254651</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:44:18</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:19:18</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>254653</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:41:56</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:11:56</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>254915</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:16:21</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:51:21</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>7</v>
+      <c r="A70" s="8" t="n">
+        <v>253361</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:03:35</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:33:35</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n">
-        <v>254715</v>
+        <v>253375</v>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
@@ -2373,26 +2369,24 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>08-09-2025 12:50:18</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>08-09-2025 13:15:18</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>254287</v>
+        <v>253368</v>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
@@ -2401,24 +2395,24 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>08-09-2025 14:07:11</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>08-09-2025 14:32:11</t>
         </is>
       </c>
       <c r="E72" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n">
-        <v>254427</v>
+        <v>253377</v>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
@@ -2427,26 +2421,24 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>09-09-2025 08:15:57</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>09-09-2025 08:40:57</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>254574</v>
+        <v>253367</v>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
@@ -2455,24 +2447,24 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>09-09-2025 10:48:40</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>09-09-2025 11:13:40</t>
         </is>
       </c>
       <c r="E74" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n">
-        <v>254187</v>
+        <v>253371</v>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
@@ -2481,12 +2473,12 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>09-09-2025 13:29:22</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:20</t>
+          <t>09-09-2025 13:54:22</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
@@ -2498,7 +2490,7 @@
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>254586</v>
+        <v>253525</v>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
@@ -2507,24 +2499,24 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 11:04:44</t>
+          <t>10-09-2025 07:42:08</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 11:29:44</t>
+          <t>10-09-2025 08:07:08</t>
         </is>
       </c>
       <c r="E76" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n">
-        <v>254166</v>
+        <v>253245</v>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
@@ -2533,24 +2525,24 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 12:21:16</t>
+          <t>10-09-2025 09:39:17</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 12:46:16</t>
+          <t>10-09-2025 10:14:17</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>254365</v>
+        <v>253401</v>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
@@ -2559,356 +2551,44 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 13:25:07</t>
+          <t>10-09-2025 12:45:07</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:07</t>
+          <t>10-09-2025 13:15:07</t>
         </is>
       </c>
       <c r="E78" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="n">
-        <v>253614</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:07:39</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:47:39</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="n">
-        <v>254903</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:50:06</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:30:06</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="n">
-        <v>254339</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:46:45</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:21:45</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="8" t="n">
-        <v>254101</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:27:43</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:57:43</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="n">
-        <v>254100</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:26:08</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:51:08</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="8" t="n">
-        <v>254252</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:19:34</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:54:34</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="n">
-        <v>253974</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:15:05</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:50:05</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="8" t="n">
-        <v>254419</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:18:30</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:53:30</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="n">
-        <v>254354</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:05:51</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:35:51</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="8" t="n">
-        <v>254547</v>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:54:31</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 11:24:31</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="n">
-        <v>253906</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 12:33:04</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>20-11-2025 13:08:04</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="9" t="n">
-        <v>254609</v>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="n">
+      <c r="A79" s="9" t="n">
         <v>252980</v>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="6" t="n">
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="9" t="n">
         <v>7</v>
       </c>
     </row>

--- a/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
@@ -38,6 +38,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
+        <bgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CCE5FF"/>
         <bgColor rgb="00CCE5FF"/>
       </patternFill>
@@ -46,24 +64,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
         <bgColor rgb="00FCE5CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD1DC"/>
-        <bgColor rgb="00EAD1DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,8 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-        <bgColor rgb="00D9D2E9"/>
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>254762</v>
+        <v>254715</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:34:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>254941</v>
+        <v>253897</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -577,12 +577,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:05:51</t>
+          <t>13-11-2025 14:46:32</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:37:51</t>
+          <t>14-11-2025 07:15:32</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>253897</v>
+        <v>254117</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -605,18 +605,16 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 14:13:21</t>
+          <t>14-11-2025 08:49:33</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 14:57:21</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 09:20:33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -624,7 +622,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>253865</v>
+        <v>253885</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -633,24 +631,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 08:31:22</t>
+          <t>14-11-2025 09:29:43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 09:13:22</t>
+          <t>14-11-2025 10:03:43</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>252061</v>
+        <v>255039</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -659,26 +657,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 11:10:08</t>
+          <t>14-11-2025 11:49:39</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:08</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 12:08:39</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>235572</v>
+        <v>255043</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -687,24 +683,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:18</t>
+          <t>14-11-2025 12:17:48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 12:32:18</t>
+          <t>14-11-2025 12:34:48</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>254605</v>
+        <v>254230</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -713,24 +709,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:17</t>
+          <t>17-11-2025 07:39:05</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 14:18:17</t>
+          <t>17-11-2025 07:54:05</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>254758</v>
+        <v>254605</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -739,12 +735,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 14:57:18</t>
+          <t>17-11-2025 08:56:34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 07:14:18</t>
+          <t>17-11-2025 09:17:34</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -756,7 +752,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>254903</v>
+        <v>254555</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -765,24 +761,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 08:15:41</t>
+          <t>17-11-2025 09:56:35</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:41</t>
+          <t>17-11-2025 10:28:35</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>254107</v>
+        <v>254276</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -791,24 +787,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 12:49:20</t>
+          <t>17-11-2025 13:21:34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 13:06:20</t>
+          <t>17-11-2025 13:57:34</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>254309</v>
+        <v>254356</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -817,44 +813,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 08:01:23</t>
+          <t>17-11-2025 14:34:36</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 08:37:23</t>
+          <t>17-11-2025 14:55:36</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>254556</v>
+        <v>243569</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 09:55:12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 07:48:00</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>18-11-2025 10:27:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>2</v>
@@ -862,339 +856,337 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>243569</v>
+        <v>235572</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:48:53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:22:53</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>254293</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>BIMEC 4</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:41:25</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 11:10:25</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:27:00</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>254941</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:45:51</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:29:51</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>254375</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:05:21</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:51:21</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>254460</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>252061</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>BIMEC 4</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 11:32:05</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 12:14:05</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>254519</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:36:38</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:03:38</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>254291</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>BIMEC 4</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:00:46</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:27:46</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:39:48</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:06:48</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>254824</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:25:39</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 13:13:39</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>254599</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:41:53</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:25:53</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>254237</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>254245</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>BIMEC 4</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:44:56</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:17:56</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>254287</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:22:01</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:55:01</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="n">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:10:47</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:35:47</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>254574</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:04:39</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:29:39</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>252811</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:23:16</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:52:16</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>254106</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:04:08</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:31:08</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>253650</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:18:47</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 12:00:47</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>254385</v>
+        <v>253961</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 13:05:35</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:00</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>18-11-2025 13:30:35</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>254165</v>
+        <v>254101</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:05</t>
+          <t>18-11-2025 14:06:30</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:05</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>18-11-2025 14:35:30</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>254117</v>
+        <v>254100</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:24</t>
+          <t>19-11-2025 07:03:55</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 10:13:24</t>
+          <t>19-11-2025 07:28:55</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>254512</v>
+        <v>254433</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 10:22:34</t>
+          <t>19-11-2025 07:57:21</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 10:39:34</t>
+          <t>19-11-2025 08:30:21</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -1206,341 +1198,341 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>254824</v>
+        <v>254354</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 11:39:07</t>
+          <t>19-11-2025 09:38:12</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 11:58:07</t>
+          <t>19-11-2025 10:09:12</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>254555</v>
+        <v>254252</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 08:26:21</t>
+          <t>19-11-2025 10:27:52</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 08:45:21</t>
+          <t>19-11-2025 10:54:52</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>244023</v>
+        <v>253906</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 11:38:20</t>
+          <t>19-11-2025 12:15:23</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 12:12:20</t>
+          <t>19-11-2025 12:44:23</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>254457</v>
+        <v>253974</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:38</t>
+          <t>19-11-2025 13:30:11</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 12:39:38</t>
+          <t>19-11-2025 14:03:11</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>254245</v>
+        <v>254419</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 12:43:34</t>
+          <t>19-11-2025 14:31:36</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 13:04:34</t>
+          <t>20-11-2025 07:00:36</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>253961</v>
+        <v>254339</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 14:34:22</t>
+          <t>20-11-2025 08:12:57</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 14:49:22</t>
+          <t>20-11-2025 08:39:57</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>254599</v>
+        <v>254547</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>19-11-2025 07:25:17</t>
+          <t>20-11-2025 12:45:55</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>19-11-2025 07:40:17</t>
+          <t>20-11-2025 13:12:55</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>254166</v>
+        <v>254967</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:21:28</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:52:28</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>254556</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>BIMEC 5</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:25:11</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:42:11</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>254546</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:21:02</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:38:02</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>7</v>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:23:00</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>254481</v>
+        <v>253382</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 10:35:25</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>253380</v>
+        <v>253865</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>14-11-2025 12:00:31</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:32:10</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 12:34:31</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>255043</v>
+        <v>254758</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 08:16:26</t>
+          <t>14-11-2025 14:31:16</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 09:00:56</t>
+          <t>14-11-2025 14:48:16</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>254189</v>
+        <v>254237</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 12:05:13</t>
+          <t>17-11-2025 07:49:39</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 12:35:43</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
+          <t>17-11-2025 08:10:39</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F39" s="4" t="n">
         <v>1</v>
@@ -1548,73 +1540,73 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>254230</v>
+        <v>254457</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 13:31:36</t>
+          <t>17-11-2025 11:14:45</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 14:02:06</t>
+          <t>17-11-2025 11:35:45</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>254433</v>
+        <v>254283</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:34</t>
+          <t>17-11-2025 11:39:40</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:35:04</t>
+          <t>17-11-2025 12:11:40</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>254276</v>
+        <v>254256</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 08:42:55</t>
+          <t>17-11-2025 13:47:26</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:25</t>
+          <t>17-11-2025 14:21:26</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -1626,21 +1618,21 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>254451</v>
+        <v>254189</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:27</t>
+          <t>18-11-2025 07:12:22</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 10:26:57</t>
+          <t>18-11-2025 07:29:22</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -1652,28 +1644,28 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>254521</v>
+        <v>254519</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 07:48:06</t>
+          <t>18-11-2025 08:25:14</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 08:22:36</t>
+          <t>18-11-2025 08:42:14</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1682,17 +1674,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 09:02:17</t>
+          <t>18-11-2025 09:59:24</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 09:34:47</t>
+          <t>18-11-2025 10:16:24</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -1703,48 +1695,50 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>253885</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="n">
+        <v>254481</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>CASON</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:39:11</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:11:41</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>8</v>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:00:00</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:32:30</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>253694</v>
+        <v>254762</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -1758,21 +1752,21 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>254129</v>
+        <v>253380</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 07:26:45</t>
+          <t>14-11-2025 07:42:31</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -1781,296 +1775,294 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>254598</v>
+        <v>254460</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:11:15</t>
+          <t>14-11-2025 09:26:48</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:15</t>
+          <t>14-11-2025 10:07:18</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>254429</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:53:59</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:26:29</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>254188</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:26:43</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:59:13</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>254437</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 08:36:40</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:07:10</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>244023</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:05:13</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:39:43</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>253838</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:48:02</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 11:20:32</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>254107</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:08:54</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:41:24</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
-        <v>254714</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:19:00</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
-        <v>254156</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:50:28</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:07:28</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n">
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>254381</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>18-11-2025 08:36:27</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:08:57</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>254675</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:34:57</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:51:57</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>254283</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:25:54</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:44:54</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>254910</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:20:40</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:37:40</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="4" t="n">
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>254756</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:32:49</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:15:19</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
         <v>7</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>253614</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>17-11-2025 08:51:12</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:23:12</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="n">
-        <v>254713</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:45:00</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n">
-        <v>254198</v>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:34:58</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:14:58</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>254256</v>
+        <v>254713</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:49:58</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 13:24:58</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>0</v>
+          <t>13-11-2025 12:45:00</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F58" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>254375</v>
+        <v>253694</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 14:15:53</t>
+          <t>13-11-2025 13:34:58</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 14:45:53</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>0</v>
+          <t>13-11-2025 14:14:58</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F59" s="6" t="n">
         <v>2</v>
@@ -2078,99 +2070,99 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>255039</v>
+        <v>253650</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 07:31:11</t>
+          <t>14-11-2025 08:16:43</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 08:01:11</t>
+          <t>14-11-2025 08:46:43</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>254381</v>
+        <v>254675</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 08:10:20</t>
+          <t>14-11-2025 13:19:51</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 08:45:20</t>
+          <t>14-11-2025 13:54:51</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>254188</v>
+        <v>254910</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 10:09:12</t>
+          <t>17-11-2025 08:28:49</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 10:39:12</t>
+          <t>17-11-2025 08:58:49</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>254437</v>
+        <v>254451</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 11:16:38</t>
+          <t>17-11-2025 10:12:21</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 11:41:38</t>
+          <t>17-11-2025 10:52:21</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
@@ -2182,47 +2174,47 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>253838</v>
+        <v>254652</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 12:39:42</t>
+          <t>18-11-2025 08:13:29</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 13:09:42</t>
+          <t>18-11-2025 08:43:29</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>250284</v>
+        <v>254598</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 14:58:04</t>
+          <t>18-11-2025 09:12:13</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>18-11-2025 07:38:04</t>
+          <t>18-11-2025 10:22:13</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
@@ -2234,205 +2226,207 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>254756</v>
+        <v>254651</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>18-11-2025 10:04:25</t>
+          <t>18-11-2025 12:06:29</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>18-11-2025 10:34:25</t>
+          <t>18-11-2025 13:21:29</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>254365</v>
+        <v>254166</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>18-11-2025 11:35:02</t>
+          <t>18-11-2025 13:44:07</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:02</t>
+          <t>18-11-2025 14:19:07</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n">
-        <v>254652</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:27:34</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:57:34</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>8</v>
+      <c r="A68" s="2" t="n">
+        <v>254385</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:34:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n">
-        <v>254429</v>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:26:18</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:56:18</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6" t="n">
+      <c r="A69" s="2" t="n">
+        <v>254198</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:26:05</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:43:05</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
-        <v>254715</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:35:00</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>2</v>
+      <c r="A70" s="2" t="n">
+        <v>253614</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:18:05</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:35:05</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="n">
-        <v>253382</v>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:49:32</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:19:32</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>2</v>
+      <c r="A71" s="2" t="n">
+        <v>254309</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:37:32</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:54:32</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>254293</v>
+        <v>254714</v>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:38</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:29:38</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="n">
-        <v>0</v>
+          <t>14-11-2025 07:50:00</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F72" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>254291</v>
+        <v>254106</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:48:29</t>
+          <t>14-11-2025 09:21:28</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>14-11-2025 13:13:29</t>
+          <t>14-11-2025 09:56:28</t>
         </is>
       </c>
       <c r="E73" s="7" t="n">
@@ -2444,21 +2438,21 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>254356</v>
+        <v>254287</v>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>14-11-2025 13:32:20</t>
+          <t>14-11-2025 11:44:07</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>14-11-2025 14:07:20</t>
+          <t>14-11-2025 12:14:07</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -2470,47 +2464,47 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>254187</v>
+        <v>254574</v>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:56</t>
+          <t>14-11-2025 14:23:45</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 09:36:56</t>
+          <t>14-11-2025 14:48:45</t>
         </is>
       </c>
       <c r="E75" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>254893</v>
+        <v>254903</v>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 10:23:20</t>
+          <t>17-11-2025 09:42:21</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:20</t>
+          <t>17-11-2025 10:17:21</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -2522,132 +2516,506 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>254586</v>
+        <v>252811</v>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 11:35:00</t>
+          <t>17-11-2025 14:34:00</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 12:00:00</t>
+          <t>18-11-2025 07:09:00</t>
         </is>
       </c>
       <c r="E77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>254915</v>
+        <v>254586</v>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 12:51:33</t>
+          <t>18-11-2025 07:20:52</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>17-11-2025 13:21:33</t>
+          <t>18-11-2025 07:55:52</t>
         </is>
       </c>
       <c r="E78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>254651</v>
+        <v>254915</v>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 08:47:25</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:17:25</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>254512</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:06:17</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:46:17</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>254521</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:45:51</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 12:20:51</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>254365</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:00:32</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:35:32</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n">
+        <v>254129</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:10:25</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:40:25</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="n">
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:35:00</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="n">
+        <v>254156</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:19:30</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:59:30</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="n">
+        <v>254165</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:26:58</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:51:58</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="n">
+        <v>250284</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:50:17</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:40:17</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="n">
+        <v>254187</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:06:38</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:56:38</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="n">
+        <v>254893</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 08:43:02</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:08:02</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="n">
+        <v>254546</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:54:42</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:24:42</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n">
         <v>254609</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t>12-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>12-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="E80" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="8" t="n">
+      <c r="E90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="9" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9" t="n">
+    <row r="91">
+      <c r="A91" s="6" t="n">
         <v>252980</v>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="E81" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="9" t="n">
+      <c r="E91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="6" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n">
+        <v>254428</v>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>254427</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>254173</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>254671</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:55:00</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
@@ -38,8 +38,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D5E8D4"/>
         <bgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -50,38 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9D2E9"/>
         <bgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD1DC"/>
-        <bgColor rgb="00EAD1DC"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -568,7 +568,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>254714</v>
+        <v>254385</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:39:30</t>
+          <t>13-11-2025 13:24:30</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>254715</v>
+        <v>253897</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -605,12 +605,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 07:10:58</t>
+          <t>13-11-2025 14:16:35</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 07:27:58</t>
+          <t>14-11-2025 07:02:35</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -619,12 +619,12 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>254429</v>
+        <v>243569</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -633,12 +633,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 09:42:31</t>
+          <t>14-11-2025 08:36:36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 10:14:31</t>
+          <t>14-11-2025 09:07:36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -650,7 +650,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>235572</v>
+        <v>254375</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 14:14:45</t>
+          <t>14-11-2025 09:29:16</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 14:29:45</t>
+          <t>14-11-2025 10:01:16</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>254893</v>
+        <v>254910</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -685,24 +685,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 07:52:44</t>
+          <t>14-11-2025 10:46:34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 08:11:44</t>
+          <t>14-11-2025 11:22:34</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>254187</v>
+        <v>254546</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -711,24 +711,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 08:58:25</t>
+          <t>14-11-2025 12:36:06</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 09:13:25</t>
+          <t>14-11-2025 13:12:06</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>254166</v>
+        <v>254187</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -737,24 +737,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 09:59:48</t>
+          <t>17-11-2025 07:01:30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 10:14:48</t>
+          <t>17-11-2025 07:18:30</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>254198</v>
+        <v>254586</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -763,24 +763,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 10:53:39</t>
+          <t>17-11-2025 08:04:54</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 11:25:39</t>
+          <t>17-11-2025 08:19:54</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>254106</v>
+        <v>254893</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -789,24 +789,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 07:00:39</t>
+          <t>17-11-2025 09:11:26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 07:34:39</t>
+          <t>17-11-2025 09:26:26</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>254915</v>
+        <v>254166</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -815,12 +815,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 09:22:18</t>
+          <t>17-11-2025 10:13:07</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 09:41:18</t>
+          <t>17-11-2025 10:28:07</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -832,7 +832,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>254651</v>
+        <v>253865</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -841,24 +841,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 10:30:10</t>
+          <t>17-11-2025 11:06:58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 10:47:10</t>
+          <t>17-11-2025 11:25:58</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>254652</v>
+        <v>254287</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -867,78 +867,76 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 11:09:49</t>
+          <t>17-11-2025 13:22:43</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 11:26:49</t>
+          <t>17-11-2025 13:41:43</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>254574</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>18-11-2025 07:51:21</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18-11-2025 08:06:21</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>253885</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:59:58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:18:58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>253897</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:52:00</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>254512</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:26:01</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:05:01</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>254117</v>
+        <v>254556</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -947,24 +945,26 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 11:04:34</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 11:31:34</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>0</v>
+          <t>14-11-2025 07:48:00</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>254653</v>
+        <v>254117</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -973,24 +973,24 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 11:40:44</t>
+          <t>14-11-2025 10:41:25</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 12:22:44</t>
+          <t>14-11-2025 11:10:25</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>252061</v>
+        <v>253614</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -999,26 +999,24 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 13:27:09</t>
+          <t>14-11-2025 11:19:35</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 13:54:09</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 12:03:35</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>254293</v>
+        <v>254309</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -1027,24 +1025,24 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 14:30:19</t>
+          <t>14-11-2025 14:06:02</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 14:57:19</t>
+          <t>14-11-2025 14:33:02</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>254291</v>
+        <v>255039</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -1053,12 +1051,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 07:16:10</t>
+          <t>18-11-2025 13:33:03</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 07:41:10</t>
+          <t>18-11-2025 14:15:03</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -1070,7 +1068,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>253865</v>
+        <v>254903</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -1079,24 +1077,24 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:01</t>
+          <t>18-11-2025 14:24:12</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 08:27:01</t>
+          <t>18-11-2025 14:53:12</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>250284</v>
+        <v>254915</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -1105,12 +1103,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 10:23:46</t>
+          <t>19-11-2025 11:09:50</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 10:54:46</t>
+          <t>19-11-2025 11:36:50</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -1122,7 +1120,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>254521</v>
+        <v>254651</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -1131,76 +1129,78 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 13:21:07</t>
+          <t>19-11-2025 12:25:43</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 13:56:07</t>
+          <t>19-11-2025 12:52:43</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>254365</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:35:48</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:04:48</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>8</v>
+      <c r="A25" s="4" t="n">
+        <v>254714</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:23:00</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>254903</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:12:20</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:41:20</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="n">
+      <c r="A26" s="4" t="n">
+        <v>254512</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:54:28</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:11:28</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>254556</v>
+        <v>254519</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
@@ -1209,26 +1209,24 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 10:11:02</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 10:43:02</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>253382</v>
+        <v>254256</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
@@ -1237,24 +1235,24 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>14-11-2025 12:00:11</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 10:35:25</t>
+          <t>14-11-2025 12:15:11</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>254283</v>
+        <v>252061</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
@@ -1263,16 +1261,18 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:31</t>
+          <t>14-11-2025 13:06:07</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 12:19:31</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
+          <t>14-11-2025 13:25:07</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F29" s="4" t="n">
         <v>2</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>254188</v>
+        <v>254293</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
@@ -1289,24 +1289,24 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:17</t>
+          <t>14-11-2025 14:01:17</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 14:27:17</t>
+          <t>14-11-2025 14:18:17</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>255039</v>
+        <v>254291</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:43</t>
+          <t>14-11-2025 14:37:08</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:21:43</t>
+          <t>14-11-2025 14:52:08</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>254375</v>
+        <v>254460</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
@@ -1341,24 +1341,24 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:30:52</t>
+          <t>17-11-2025 07:10:59</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:47:52</t>
+          <t>17-11-2025 07:29:59</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>254256</v>
+        <v>254237</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
@@ -1367,24 +1367,26 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 08:33:10</t>
+          <t>17-11-2025 08:16:40</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 08:50:10</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
+          <t>17-11-2025 08:37:40</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>254519</v>
+        <v>254605</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
@@ -1393,24 +1395,24 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 09:41:05</t>
+          <t>17-11-2025 11:41:45</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 09:56:05</t>
+          <t>17-11-2025 12:00:45</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>254460</v>
+        <v>254198</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
@@ -1419,24 +1421,24 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 11:13:15</t>
+          <t>17-11-2025 12:39:47</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 11:30:15</t>
+          <t>17-11-2025 13:15:47</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>254605</v>
+        <v>254107</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
@@ -1445,24 +1447,24 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 12:16:56</t>
+          <t>18-11-2025 08:50:47</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 12:33:56</t>
+          <t>18-11-2025 09:24:47</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>254758</v>
+        <v>254365</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
@@ -1471,130 +1473,134 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 13:12:57</t>
+          <t>18-11-2025 12:19:50</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 13:29:57</t>
+          <t>18-11-2025 12:36:50</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>254481</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:00:00</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:32:30</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>254237</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:31:20</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:52:20</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>254762</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 13:53:40</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 14:28:10</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>254356</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:56:26</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:17:26</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>4</v>
+      <c r="F39" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>253614</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:17:02</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:49:02</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="n">
+      <c r="A40" s="5" t="n">
+        <v>253380</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:01</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:42:31</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>253885</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:51:29</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:25:29</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>8</v>
+      <c r="A41" s="5" t="n">
+        <v>255043</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:26:48</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:11:18</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>254481</v>
+        <v>254433</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -1603,18 +1609,16 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 13:15:35</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 13:46:05</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>1</v>
@@ -1622,7 +1626,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>253380</v>
+        <v>254189</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -1631,26 +1635,24 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>14-11-2025 14:53:56</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 14:32:10</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>17-11-2025 07:24:26</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>244023</v>
+        <v>254230</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -1659,24 +1661,24 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:16:26</t>
+          <t>17-11-2025 08:20:18</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:52:56</t>
+          <t>17-11-2025 08:50:48</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>254230</v>
+        <v>254457</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -1685,24 +1687,24 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:01:15</t>
+          <t>17-11-2025 09:53:17</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:39:45</t>
+          <t>17-11-2025 10:27:47</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>254189</v>
+        <v>254276</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -1711,24 +1713,24 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 10:42:13</t>
+          <t>17-11-2025 10:31:42</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 11:12:43</t>
+          <t>17-11-2025 11:08:12</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>254433</v>
+        <v>253838</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
@@ -1737,24 +1739,24 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 12:08:36</t>
+          <t>17-11-2025 11:45:14</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 12:39:06</t>
+          <t>17-11-2025 12:17:44</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>255043</v>
+        <v>254599</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
@@ -1763,24 +1765,24 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 13:46:57</t>
+          <t>17-11-2025 14:06:06</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 14:17:27</t>
+          <t>17-11-2025 14:38:36</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>254586</v>
+        <v>254653</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
@@ -1789,24 +1791,24 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 09:21:44</t>
+          <t>18-11-2025 07:23:30</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:14</t>
+          <t>18-11-2025 08:00:00</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>254276</v>
+        <v>252811</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
@@ -1815,24 +1817,24 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 10:45:46</t>
+          <t>18-11-2025 09:04:25</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 11:18:16</t>
+          <t>18-11-2025 09:36:55</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>253838</v>
+        <v>254521</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -1841,24 +1843,24 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 11:55:18</t>
+          <t>18-11-2025 09:48:47</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 12:27:48</t>
+          <t>18-11-2025 10:23:17</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>252811</v>
+        <v>254598</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -1867,12 +1869,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 14:16:10</t>
+          <t>18-11-2025 11:02:58</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 14:54:40</t>
+          <t>18-11-2025 11:53:28</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -1883,60 +1885,64 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>254756</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:06:33</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:45:03</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>7</v>
+      <c r="A53" s="6" t="n">
+        <v>254129</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:00:00</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:45:00</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>254107</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:45:40</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:26:10</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>7</v>
+      <c r="A54" s="6" t="n">
+        <v>254715</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>13-11-2025 13:29:30</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>13-11-2025 14:09:30</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>254762</v>
+        <v>244023</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
@@ -1945,26 +1951,24 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 08:24:02</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 12:30:00</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 09:09:02</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>253694</v>
+        <v>254429</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
@@ -1973,18 +1977,16 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 13:01:51</t>
+          <t>14-11-2025 09:17:21</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 13:41:51</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 09:47:21</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>2</v>
@@ -1992,7 +1994,7 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>254598</v>
+        <v>254758</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
@@ -2001,766 +2003,764 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 07:43:37</t>
+          <t>14-11-2025 13:47:35</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:03:37</t>
+          <t>14-11-2025 14:17:35</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>254356</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:18:58</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:58:58</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>235572</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:58:34</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 11:28:34</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
+        <v>254188</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 12:51:33</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:21:33</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>254437</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:59:00</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:24:00</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>254381</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 07:22:03</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 07:52:03</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="6" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>254129</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>253961</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:15:55</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:45:55</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>254245</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:21:50</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:46:50</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>254756</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 12:16:38</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:06:38</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>250284</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:07:16</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:37:16</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>253694</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>14-11-2025 07:17:00</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="F67" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>254385</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>254156</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:01:30</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:33:30</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:18:45</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:39:45</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="F68" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>254283</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:07:14</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:24:14</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>254309</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>253382</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:25:35</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:42:35</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3" t="n">
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 13:00:00</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 13:19:00</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>254824</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:44:06</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:01:06</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>254675</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:29:19</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:46:19</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>243569</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>254555</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:42:36</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:14:36</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="n">
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:20:17</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:37:17</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>254555</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:36:16</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:53:16</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>254165</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:45:00</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>254451</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:43:19</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:18:19</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>253650</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:39:27</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:19:27</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>254165</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>254106</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 11:52:35</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 12:27:35</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>254652</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:15:14</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:55:14</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>254713</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:45:00</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:35:00</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F79" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n">
+        <v>254609</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>252980</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="9" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>254156</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:43:19</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:08:19</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="8" t="n">
+        <v>254427</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F64" s="7" t="n">
+      <c r="F82" s="8" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>254824</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:35:47</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 11:10:47</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="7" t="n">
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>254428</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>254910</v>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:39:01</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:14:01</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7" t="n">
+    <row r="84">
+      <c r="A84" s="9" t="n">
+        <v>254173</v>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="9" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>254381</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:27:33</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:02:33</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>254245</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:26:25</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:56:25</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>253961</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:26:13</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:51:13</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="n">
-        <v>254546</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:27:08</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:07:08</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="n">
-        <v>254713</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>254967</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:35:00</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="n">
-        <v>254451</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:24:58</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:59:58</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="n">
-        <v>253650</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:21:06</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:01:06</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="n">
-        <v>254675</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:34:14</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>17-11-2025 12:09:14</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="n">
-        <v>254599</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:43:12</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:18:12</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="n">
-        <v>254457</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C76" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:03:06</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:43:06</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="n">
-        <v>254437</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:47:01</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:12:01</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="8" t="n">
-        <v>254287</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:10:05</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:40:05</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="n">
-        <v>254574</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C79" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 12:49:43</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:14:43</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="n">
-        <v>254609</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>252980</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="n">
-        <v>254427</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="n">
-        <v>254428</v>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>254173</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>254967</v>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>20-11-2025 14:00:00</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>20-11-2025 14:29:00</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="n">
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:30:00</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>253974</v>
+        <v>254101</v>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>19-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>19-11-2025 14:21:00</t>
+          <t>18-11-2025 14:25:00</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -2786,7 +2786,7 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>254100</v>
+        <v>253974</v>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>19-11-2025 14:49:25</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>20-11-2025 07:04:25</t>
+          <t>19-11-2025 14:15:00</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -2812,59 +2812,59 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>254101</v>
+        <v>254671</v>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>20-11-2025 07:32:51</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>20-11-2025 07:47:51</t>
+          <t>18-11-2025 14:45:00</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>254354</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:29:00</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="n">
-        <v>254671</v>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:45:00</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>254354</v>
+        <v>254100</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 14:19:00</t>
+          <t>18-11-2025 14:21:00</t>
         </is>
       </c>
       <c r="E90" s="2" t="n">
@@ -2915,54 +2915,54 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="n">
+      <c r="A92" s="6" t="n">
         <v>254339</v>
       </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>18-11-2025 14:00:00</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:35:00</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="8" t="n">
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:40:00</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="6" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="n">
+      <c r="A93" s="3" t="n">
         <v>254419</v>
       </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:40:00</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="7" t="n">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:47:40</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>19-11-2025 07:14:40</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>19-11-2025 14:17:00</t>
+          <t>19-11-2025 14:19:00</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
@@ -2993,28 +2993,28 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="5" t="n">
         <v>253906</v>
       </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:52:20</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:27:20</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="7" t="n">
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>19-11-2025 07:57:01</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>19-11-2025 08:31:31</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5" t="n">
         <v>7</v>
       </c>
     </row>

--- a/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
@@ -38,14 +38,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD1DC"/>
-        <bgColor rgb="00EAD1DC"/>
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCE5FF"/>
+        <bgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -56,32 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CCE5FF"/>
-        <bgColor rgb="00CCE5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9D2E9"/>
         <bgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -568,7 +568,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>254385</v>
+        <v>254715</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:24:30</t>
+          <t>13-11-2025 13:43:30</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>253897</v>
+        <v>254556</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -605,12 +605,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13-11-2025 14:16:35</t>
+          <t>14-11-2025 07:58:02</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 07:02:35</t>
+          <t>14-11-2025 08:15:02</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -619,12 +619,12 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>254230</v>
+        <v>254910</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -633,24 +633,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 08:36:36</t>
+          <t>14-11-2025 11:08:27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 09:24:36</t>
+          <t>14-11-2025 11:25:27</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>254433</v>
+        <v>254915</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 10:27:04</t>
+          <t>14-11-2025 12:38:59</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 10:42:04</t>
+          <t>14-11-2025 13:12:59</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>254189</v>
+        <v>254758</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -685,12 +685,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 11:49:55</t>
+          <t>14-11-2025 14:01:52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 12:04:55</t>
+          <t>14-11-2025 14:20:52</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -702,7 +702,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>255043</v>
+        <v>254117</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -711,24 +711,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 13:00:48</t>
+          <t>17-11-2025 07:22:15</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14-11-2025 13:15:48</t>
+          <t>17-11-2025 07:54:15</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>254457</v>
+        <v>254512</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -737,12 +737,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 08:20:05</t>
+          <t>17-11-2025 08:03:25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 08:39:05</t>
+          <t>17-11-2025 08:20:25</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -754,7 +754,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>254187</v>
+        <v>254519</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -763,24 +763,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 08:43:00</t>
+          <t>17-11-2025 09:19:58</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 09:00:00</t>
+          <t>17-11-2025 09:51:58</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>254893</v>
+        <v>254256</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -789,24 +789,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 09:46:24</t>
+          <t>17-11-2025 11:09:08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 10:01:24</t>
+          <t>17-11-2025 11:24:08</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>254586</v>
+        <v>254375</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -815,24 +815,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:04</t>
+          <t>17-11-2025 12:15:03</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 11:03:04</t>
+          <t>17-11-2025 12:32:03</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>254166</v>
+        <v>254187</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -841,24 +841,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 11:54:37</t>
+          <t>17-11-2025 13:17:21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:37</t>
+          <t>17-11-2025 13:34:21</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>254521</v>
+        <v>254245</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -867,24 +867,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 12:48:28</t>
+          <t>17-11-2025 14:20:44</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 13:07:28</t>
+          <t>17-11-2025 14:37:44</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>254653</v>
+        <v>254521</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -893,12 +893,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 13:47:09</t>
+          <t>18-11-2025 08:07:32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17-11-2025 14:04:09</t>
+          <t>18-11-2025 08:24:32</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -910,7 +910,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>252811</v>
+        <v>254106</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -919,12 +919,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 07:08:33</t>
+          <t>18-11-2025 09:04:13</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 07:25:33</t>
+          <t>18-11-2025 09:21:13</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -936,7 +936,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>254915</v>
+        <v>253885</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -945,50 +945,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 07:37:26</t>
+          <t>18-11-2025 11:08:52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18-11-2025 07:58:26</t>
+          <t>18-11-2025 11:25:52</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>253885</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:47:18</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:04:18</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>8</v>
+      <c r="A18" s="3" t="n">
+        <v>254129</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:42:00</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>254556</v>
+        <v>254291</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -997,26 +999,24 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 08:26:30</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:48:00</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 09:10:30</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>254460</v>
+        <v>252061</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -1025,24 +1025,26 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 10:41:25</t>
+          <t>14-11-2025 09:29:21</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 11:23:25</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
+          <t>14-11-2025 09:56:21</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>253865</v>
+        <v>254293</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -1051,24 +1053,24 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 12:10:06</t>
+          <t>14-11-2025 10:32:31</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 12:37:06</t>
+          <t>14-11-2025 10:59:31</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>254605</v>
+        <v>253865</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -1077,24 +1079,24 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>14-11-2025 14:33:51</t>
+          <t>14-11-2025 11:18:22</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 07:06:51</t>
+          <t>14-11-2025 11:45:22</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>254237</v>
+        <v>254451</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -1103,18 +1105,16 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:53</t>
+          <t>14-11-2025 13:42:07</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 08:14:53</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 14:11:07</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>1</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>254758</v>
+        <v>254555</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -1131,24 +1131,24 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 11:18:58</t>
+          <t>17-11-2025 11:32:16</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 11:49:58</t>
+          <t>17-11-2025 12:14:16</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>253382</v>
+        <v>253650</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 12:51:21</t>
+          <t>18-11-2025 07:07:15</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 13:33:21</t>
+          <t>18-11-2025 07:34:15</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
@@ -1174,7 +1174,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>254117</v>
+        <v>254652</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -1183,180 +1183,182 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>17-11-2025 14:58:27</t>
+          <t>18-11-2025 12:07:23</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>18-11-2025 07:27:27</t>
+          <t>18-11-2025 12:49:23</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>254675</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:36:37</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:05:37</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>1</v>
+      <c r="A27" s="4" t="n">
+        <v>254714</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:23:00</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>254512</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:39:35</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:06:35</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
+      <c r="A28" s="4" t="n">
+        <v>253382</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:54:28</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:13:28</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>254287</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 12:06:08</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 12:48:08</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n">
+      <c r="A29" s="4" t="n">
+        <v>243569</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:38:34</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:57:34</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>255039</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:19:15</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:53:15</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>254824</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:02:24</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:34:24</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>254599</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:02:37</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:36:37</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>250284</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:57:46</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:32:46</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>254106</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:59:07</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 10:32:07</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>254651</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 4</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:19:46</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:46:46</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>253694</v>
+        <v>254356</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
@@ -1365,26 +1367,24 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 10:21:31</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:21:00</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>18-11-2025 10:36:31</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>254283</v>
+        <v>253961</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
@@ -1393,24 +1393,24 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 09:22:45</t>
+          <t>18-11-2025 13:36:07</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 09:39:45</t>
+          <t>18-11-2025 13:51:07</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>254910</v>
+        <v>254101</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
@@ -1419,24 +1419,24 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 11:15:31</t>
+          <t>18-11-2025 14:27:02</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 11:32:31</t>
+          <t>18-11-2025 14:46:02</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>243569</v>
+        <v>253974</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 12:46:03</t>
+          <t>19-11-2025 07:14:28</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 13:03:03</t>
+          <t>19-11-2025 07:29:28</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>252061</v>
+        <v>254100</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
@@ -1471,18 +1471,16 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 13:24:44</t>
+          <t>19-11-2025 07:57:53</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 13:58:44</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>19-11-2025 08:12:53</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>2</v>
@@ -1490,7 +1488,7 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>254293</v>
+        <v>254354</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
@@ -1499,24 +1497,24 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 14:34:54</t>
+          <t>19-11-2025 08:41:19</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>14-11-2025 14:51:54</t>
+          <t>19-11-2025 08:58:19</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>253650</v>
+        <v>254252</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
@@ -1525,24 +1523,24 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:10:45</t>
+          <t>19-11-2025 09:16:59</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 07:46:45</t>
+          <t>19-11-2025 09:33:59</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>254437</v>
+        <v>254339</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
@@ -1551,24 +1549,24 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 12:19:53</t>
+          <t>19-11-2025 10:54:30</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 12:51:53</t>
+          <t>19-11-2025 11:11:30</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>254375</v>
+        <v>254547</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
@@ -1577,24 +1575,24 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 13:49:56</t>
+          <t>20-11-2025 07:17:28</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 14:10:56</t>
+          <t>20-11-2025 07:34:28</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>244023</v>
+        <v>254419</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
@@ -1603,24 +1601,24 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>17-11-2025 14:56:14</t>
+          <t>20-11-2025 08:43:01</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 07:15:14</t>
+          <t>20-11-2025 09:04:01</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>254276</v>
+        <v>253906</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
@@ -1629,154 +1627,160 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 07:23:32</t>
+          <t>20-11-2025 10:16:22</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>18-11-2025 07:42:32</t>
+          <t>20-11-2025 10:35:22</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>254546</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:19:34</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:34:34</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="n">
+      <c r="A44" s="5" t="n">
+        <v>254481</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:00:00</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:32:30</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>254762</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 13:53:40</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>13-11-2025 14:28:10</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>253380</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:01</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:42:31</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>255039</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:23:59</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:40:59</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>254599</v>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:50:08</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:07:08</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>254903</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:52:02</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>18-11-2025 12:09:02</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="n">
+      <c r="A47" s="5" t="n">
+        <v>255043</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:26:48</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:11:18</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>254433</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 13:15:35</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>14-11-2025 13:46:05</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>254652</v>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:25:40</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:42:40</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>254481</v>
+        <v>254189</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
@@ -1785,18 +1789,16 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 14:53:56</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>17-11-2025 07:24:26</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>1</v>
@@ -1804,7 +1806,7 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>253380</v>
+        <v>254230</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
@@ -1813,26 +1815,24 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>17-11-2025 08:20:18</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>13-11-2025 14:32:10</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>17-11-2025 08:50:48</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>254107</v>
+        <v>254460</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -1841,24 +1841,24 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:16:26</t>
+          <t>17-11-2025 09:53:17</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:56:56</t>
+          <t>17-11-2025 10:27:47</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>254256</v>
+        <v>254287</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 11:52:00</t>
+          <t>17-11-2025 11:14:28</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 12:24:30</t>
+          <t>17-11-2025 11:46:58</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -1884,7 +1884,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>254519</v>
+        <v>254574</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
@@ -1893,24 +1893,24 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 13:15:25</t>
+          <t>17-11-2025 13:56:36</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>14-11-2025 13:45:55</t>
+          <t>17-11-2025 14:27:06</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>254356</v>
+        <v>254598</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -1919,154 +1919,158 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:05</t>
+          <t>18-11-2025 09:20:42</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>17-11-2025 07:35:35</t>
+          <t>18-11-2025 10:11:12</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
-        <v>254245</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:35:11</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:05:41</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>4</v>
+      <c r="A55" s="6" t="n">
+        <v>253694</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:00:00</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>13-11-2025 12:45:00</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
-        <v>254381</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>17-11-2025 12:35:29</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:07:59</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>7</v>
+      <c r="A56" s="6" t="n">
+        <v>253897</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>13-11-2025 14:46:45</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:46:45</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
-        <v>254188</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:31:51</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:04:21</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
+      <c r="A57" s="6" t="n">
+        <v>254283</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:20:46</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:15:46</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
+        <v>244023</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:51:32</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:31:32</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="n">
-        <v>254574</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:41:47</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:14:17</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
-        <v>254598</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:07:54</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:58:24</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>7</v>
+      <c r="A59" s="6" t="n">
+        <v>254651</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:39:51</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 13:19:51</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>254713</v>
+        <v>254893</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
@@ -2075,26 +2079,24 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 13:42:29</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>14-11-2025 14:17:29</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>254762</v>
+        <v>254586</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
@@ -2103,26 +2105,24 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 13:34:58</t>
+          <t>17-11-2025 07:04:10</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 14:14:58</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>17-11-2025 07:29:10</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>254129</v>
+        <v>254237</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:49</t>
+          <t>17-11-2025 08:20:42</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 07:26:49</t>
+          <t>17-11-2025 09:05:42</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2145,12 +2145,12 @@
         </is>
       </c>
       <c r="F62" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>254429</v>
+        <v>253838</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
@@ -2159,24 +2159,24 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:11:19</t>
+          <t>17-11-2025 12:09:48</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:51:19</t>
+          <t>17-11-2025 12:44:48</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>235572</v>
+        <v>254107</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
@@ -2185,24 +2185,24 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:51:34</t>
+          <t>17-11-2025 14:33:10</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 13:16:34</t>
+          <t>18-11-2025 07:03:10</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>254555</v>
+        <v>254381</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
@@ -2211,810 +2211,810 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>14-11-2025 14:39:33</t>
+          <t>18-11-2025 09:58:13</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>17-11-2025 07:19:33</t>
+          <t>18-11-2025 10:28:13</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
+        <v>254713</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:00</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>254156</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:06:58</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:27:58</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>254165</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:55:26</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:10:26</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>254198</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:08:45</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:42:45</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>254309</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:17:45</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:36:45</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>254429</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:45:00</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>235572</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:45:14</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:10:14</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>254605</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 13:33:13</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:18:13</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>254653</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:57:15</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:27:15</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>254276</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>17-11-2025 08:31:39</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:11:39</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>253614</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:48:41</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:23:41</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>254385</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:35:00</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>254546</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:27:05</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:02:05</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>254675</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:51:29</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:26:29</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>254188</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:00:27</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:35:27</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>254437</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:12:53</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:37:53</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>254903</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 08:35:57</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:05:57</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>254756</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:22:35</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:17:35</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>250284</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 07:18:13</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 07:48:13</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>252811</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:14:34</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:54:34</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
         <v>254365</v>
       </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:12:32</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:52:32</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="6" t="n">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:06:26</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:51:26</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>254715</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>254457</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 12:58:58</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:28:58</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>254166</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:32:54</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:02:54</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="n">
+        <v>254609</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>252980</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:17:00</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="n">
+        <v>254427</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F67" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>254198</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:31:32</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:05:32</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>253614</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:40:32</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:57:32</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="7" t="n">
+      <c r="F91" s="8" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="n">
-        <v>254714</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="9" t="n">
+        <v>254428</v>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>254173</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>254967</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>BIMEC 4</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:29:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>254671</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:50:00</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="n">
-        <v>254156</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:21:28</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:51:28</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="n">
-        <v>254824</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 11:18:57</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>14-11-2025 11:53:57</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="n">
-        <v>253961</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:22:10</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:02:10</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="n">
-        <v>254756</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:38:05</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:28:05</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>254165</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:35:00</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>254451</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:33:19</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:08:19</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>254291</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:29:27</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:09:27</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>253838</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:28:18</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:58:18</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>254309</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:46:40</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:21:40</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>254354</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:21:41</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 09:56:41</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>254100</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 10:15:22</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 10:45:22</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>254101</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:13:47</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:38:47</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>254252</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:07:13</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:42:13</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>253974</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 14:02:44</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>19-11-2025 14:37:44</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>254547</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:06:09</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:41:09</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>253906</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:49:42</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>20-11-2025 09:24:42</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>254339</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:10:30</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:50:30</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>254967</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>20-11-2025 14:56:28</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>21-11-2025 07:26:28</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>254419</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>21-11-2025 11:46:53</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>21-11-2025 12:26:53</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="n">
-        <v>254609</v>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="n">
-        <v>252980</v>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="n">
-        <v>254427</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="n">
-        <v>254428</v>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="n">
-        <v>254173</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="n">
-        <v>254671</v>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>18-11-2025 14:00:00</t>
         </is>
       </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:36:30</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="5" t="n">
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:40:00</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
+++ b/PS-VRP/Dati_output/schedulazione_ridotta.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CCE5FF"/>
         <bgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +100,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -504,7 +513,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>252207</v>
+        <v>252723</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -530,7 +539,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>252723</v>
+        <v>252207</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
@@ -539,12 +548,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>08-07-2025 13:08:33</t>
+          <t>08-07-2025 14:50:57</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>08-07-2025 13:23:33</t>
+          <t>09-07-2025 07:05:57</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -556,7 +565,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>252890</v>
+        <v>252680</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -570,19 +579,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 08:16:30</t>
+          <t>09-07-2025 08:14:30</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>252371</v>
+        <v>252210</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -591,12 +600,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 09:08:12</t>
+          <t>09-07-2025 12:29:12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 09:25:12</t>
+          <t>09-07-2025 12:46:12</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -608,7 +617,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>243527</v>
+        <v>252209</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -617,18 +626,16 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 10:15:15</t>
+          <t>09-07-2025 13:15:24</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 10:32:15</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>09-07-2025 13:30:24</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -636,7 +643,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>243523</v>
+        <v>252371</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -645,18 +652,16 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 11:38:52</t>
+          <t>09-07-2025 13:59:36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 11:53:52</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>09-07-2025 14:16:36</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -664,7 +669,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>251790</v>
+        <v>243569</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -673,26 +678,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 13:00:29</t>
+          <t>10-07-2025 07:06:38</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>09-07-2025 13:15:29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>10-07-2025 07:23:38</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>243536</v>
+        <v>252814</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -701,26 +704,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 09:10:32</t>
+          <t>10-07-2025 07:45:19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 09:25:32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>10-07-2025 08:02:19</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>243526</v>
+        <v>252362</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -729,26 +730,24 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 10:32:09</t>
+          <t>10-07-2025 08:52:24</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 10:47:09</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>10-07-2025 09:09:24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>243535</v>
+        <v>252378</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -757,26 +756,24 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 11:53:46</t>
+          <t>10-07-2025 09:49:21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 12:08:46</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>10-07-2025 10:04:21</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>252680</v>
+        <v>252298</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -785,24 +782,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 13:15:23</t>
+          <t>10-07-2025 10:41:54</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10-07-2025 13:32:23</t>
+          <t>10-07-2025 10:58:54</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>252210</v>
+        <v>250383</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -811,24 +808,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 09:47:05</t>
+          <t>10-07-2025 12:09:40</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 10:04:05</t>
+          <t>10-07-2025 12:26:40</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>252209</v>
+        <v>252495</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
@@ -837,24 +834,24 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 10:33:17</t>
+          <t>10-07-2025 12:51:36</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 10:48:17</t>
+          <t>10-07-2025 13:08:36</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>252814</v>
+        <v>252519</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -863,12 +860,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 11:17:29</t>
+          <t>10-07-2025 14:19:22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 11:34:29</t>
+          <t>10-07-2025 14:36:22</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -880,7 +877,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>252519</v>
+        <v>252890</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -889,24 +886,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 12:24:34</t>
+          <t>10-07-2025 14:47:51</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 12:41:34</t>
+          <t>11-07-2025 07:06:51</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>252495</v>
+        <v>251812</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
@@ -915,24 +912,24 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 12:53:02</t>
+          <t>11-07-2025 07:58:33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 13:10:02</t>
+          <t>11-07-2025 08:17:33</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>252201</v>
+        <v>252369</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -941,12 +938,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 14:20:49</t>
+          <t>11-07-2025 08:51:25</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11-07-2025 14:37:49</t>
+          <t>11-07-2025 09:18:25</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -957,380 +954,378 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>243569</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>08-07-2025 12:00:00</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>08-07-2025 12:17:00</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="n">
+      <c r="A19" s="2" t="n">
+        <v>250284</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2025 09:37:37</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2025 10:09:37</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>252783</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2025 12:35:58</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2025 12:54:58</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>252467</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2025 13:06:55</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2025 13:23:55</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>252476</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>11-07-2025 14:45:05</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 07:04:05</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>252665</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 08:16:26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 08:33:26</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>252277</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 09:22:18</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 09:39:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>252350</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 12:04:14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 12:21:14</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>252598</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 13:13:07</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>14-07-2025 13:28:07</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>252978</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>08-07-2025 12:38:40</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>08-07-2025 12:57:40</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="n">
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>252576</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2025 07:57:44</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2025 08:12:44</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>252298</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>08-07-2025 13:20:58</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>08-07-2025 13:41:58</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>252378</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>08-07-2025 14:52:44</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 07:09:44</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="n">
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>252779</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2025 14:26:48</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2025 14:41:48</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>252362</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 07:47:18</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 08:02:18</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="n">
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>252899</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2025 09:46:05</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2025 10:03:05</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>251812</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 08:42:15</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 09:01:15</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>250383</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 09:35:07</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 09:54:07</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3" t="n">
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>252426</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2025 13:03:39</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2025 13:20:39</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>252369</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 10:19:03</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 10:42:03</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>250284</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 11:01:15</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 11:33:15</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3" t="n">
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>252778</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2025 08:24:56</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2025 08:43:56</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>252157</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>BIMEC 3</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2025 11:24:56</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2025 11:49:56</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>252783</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 13:59:36</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 14:18:36</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>252784</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 14:30:33</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>09-07-2025 14:45:33</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>252785</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>10-07-2025 07:12:31</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>10-07-2025 07:27:31</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>235572</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>10-07-2025 08:25:52</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>10-07-2025 08:42:52</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>251685</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>10-07-2025 10:05:51</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>10-07-2025 10:22:51</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>252456</v>
+        <v>252201</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -1339,26 +1334,24 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>10-07-2025 12:01:36</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10-07-2025 12:18:36</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>08-07-2025 12:17:00</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>244023</v>
+        <v>252999</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -1367,24 +1360,24 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>10-07-2025 14:43:04</t>
+          <t>08-07-2025 12:51:06</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 07:00:04</t>
+          <t>08-07-2025 13:23:06</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>252467</v>
+        <v>252087</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -1393,24 +1386,24 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 07:08:22</t>
+          <t>09-07-2025 10:48:57</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 07:25:22</t>
+          <t>09-07-2025 11:05:57</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>252790</v>
+        <v>251849</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -1419,24 +1412,26 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 08:46:32</t>
+          <t>09-07-2025 11:41:27</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 09:01:32</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>0</v>
+          <t>09-07-2025 12:00:27</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>252336</v>
+        <v>252220</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1445,24 +1440,24 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 09:13:39</t>
+          <t>09-07-2025 12:33:50</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 09:28:39</t>
+          <t>09-07-2025 12:50:50</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>252755</v>
+        <v>235572</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -1471,24 +1466,24 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 11:28:55</t>
+          <t>09-07-2025 14:11:21</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 11:45:55</t>
+          <t>09-07-2025 14:28:21</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>252087</v>
+        <v>244023</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -1497,24 +1492,24 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 13:35:30</t>
+          <t>10-07-2025 07:51:20</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 13:52:30</t>
+          <t>10-07-2025 08:08:20</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>252350</v>
+        <v>252638</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -1523,26 +1518,24 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 14:28:00</t>
+          <t>10-07-2025 08:16:38</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>11-07-2025 14:45:00</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+          <t>10-07-2025 08:33:38</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>252598</v>
+        <v>252085</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -1551,24 +1544,24 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>14-07-2025 07:36:53</t>
+          <t>10-07-2025 09:35:08</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>14-07-2025 07:51:53</t>
+          <t>10-07-2025 09:52:08</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>252662</v>
+        <v>252549</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -1577,24 +1570,24 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>14-07-2025 10:21:30</t>
+          <t>10-07-2025 10:20:41</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>14-07-2025 10:36:30</t>
+          <t>10-07-2025 10:37:41</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>252426</v>
+        <v>252662</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -1603,12 +1596,12 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>14-07-2025 13:46:22</t>
+          <t>10-07-2025 12:10:16</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>14-07-2025 14:01:22</t>
+          <t>10-07-2025 12:27:16</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
@@ -1620,7 +1613,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>252473</v>
+        <v>252656</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -1629,12 +1622,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>15-07-2025 09:05:39</t>
+          <t>11-07-2025 07:37:08</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>15-07-2025 09:20:39</t>
+          <t>11-07-2025 07:52:08</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
@@ -1646,7 +1639,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>252656</v>
+        <v>252473</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -1655,12 +1648,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>15-07-2025 12:30:31</t>
+          <t>11-07-2025 11:02:00</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>15-07-2025 12:45:31</t>
+          <t>11-07-2025 11:17:00</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
@@ -1672,7 +1665,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>252899</v>
+        <v>252790</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -1681,12 +1674,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>16-07-2025 07:55:23</t>
+          <t>11-07-2025 14:26:52</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>16-07-2025 08:12:23</t>
+          <t>11-07-2025 14:47:52</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -1698,7 +1691,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>252476</v>
+        <v>252336</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -1707,19 +1700,19 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>16-07-2025 11:12:57</t>
+          <t>11-07-2025 14:59:59</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>16-07-2025 11:27:57</t>
+          <t>14-07-2025 07:14:59</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1733,12 +1726,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>16-07-2025 12:40:18</t>
+          <t>14-07-2025 09:15:15</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>16-07-2025 12:57:18</t>
+          <t>14-07-2025 09:32:15</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
@@ -1750,7 +1743,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>252547</v>
+        <v>252470</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -1759,24 +1752,24 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>16-07-2025 14:53:47</t>
+          <t>14-07-2025 11:28:44</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>17-07-2025 07:10:47</t>
+          <t>14-07-2025 11:49:44</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>251231</v>
+        <v>252334</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -1785,467 +1778,473 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>17-07-2025 08:31:57</t>
+          <t>14-07-2025 12:52:14</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>17-07-2025 08:48:57</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
+          <t>14-07-2025 13:09:14</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>252713</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>08-07-2025 12:00:00</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>08-07-2025 12:34:30</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>252456</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>10-07-2025 11:42:16</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>10-07-2025 12:20:46</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>252334</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2025 14:01:15</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2025 14:18:15</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
+      <c r="F52" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>252755</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>10-07-2025 14:45:13</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 07:17:43</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>252470</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>18-07-2025 14:24:51</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>18-07-2025 14:41:51</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>251495</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 09:07:18</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 09:39:48</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>252549</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 07:44:21</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 08:01:21</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>251926</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 10:52:08</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 11:24:38</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>252665</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 09:33:56</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 09:50:56</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>252414</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 12:43:33</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 13:20:03</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>252277</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 10:39:49</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 10:56:49</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>252511</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>11-07-2025 14:37:13</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>14-07-2025 07:13:43</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>252507</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>14-07-2025 08:41:10</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>14-07-2025 09:11:40</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>252978</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>08-07-2025 12:00:00</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>08-07-2025 12:19:00</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>251919</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>08-07-2025 12:42:18</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>08-07-2025 13:16:18</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>252245</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>09-07-2025 07:36:21</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>09-07-2025 07:53:21</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>252686</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>10-07-2025 08:03:06</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>10-07-2025 08:20:06</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>243536</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>10-07-2025 13:49:15</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>10-07-2025 14:23:15</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>252085</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 13:21:44</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 13:38:44</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>251849</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 14:07:17</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 14:24:17</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="F63" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>243523</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 07:29:52</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 07:44:52</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>252220</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>21-07-2025 14:57:40</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>22-07-2025 07:14:40</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>251495</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>22-07-2025 08:35:11</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>22-07-2025 08:52:11</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>252157</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>22-07-2025 10:04:32</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>22-07-2025 10:27:32</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>252999</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>08-07-2025 12:00:00</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>08-07-2025 12:32:30</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>252713</v>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>09-07-2025 09:58:20</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>09-07-2025 10:34:50</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>251926</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>11-07-2025 09:42:36</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>11-07-2025 10:15:06</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>252638</v>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>11-07-2025 11:34:01</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>11-07-2025 12:06:31</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>7</v>
+      <c r="F64" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>252414</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>11-07-2025 13:08:01</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>11-07-2025 13:42:31</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>7</v>
+      <c r="A65" s="5" t="n">
+        <v>243535</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 08:51:29</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 09:06:29</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
-        <v>252507</v>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>11-07-2025 14:59:40</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>14-07-2025 07:36:10</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="4" t="n">
-        <v>7</v>
+      <c r="A66" s="5" t="n">
+        <v>243526</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 10:13:06</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 10:28:06</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>252511</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>14-07-2025 09:19:03</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>14-07-2025 09:49:33</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="4" t="n">
-        <v>7</v>
+      <c r="A67" s="5" t="n">
+        <v>243527</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 11:34:43</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 11:49:43</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2259,227 +2258,237 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
+          <t>11-07-2025 12:56:20</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>11-07-2025 13:13:20</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>245623</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
           <t>08-07-2025 12:00:00</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>08-07-2025 12:17:00</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="n">
-        <v>251919</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>08-07-2025 12:30:00</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>251790</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>09-07-2025 08:10:09</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>09-07-2025 08:45:09</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>252784</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>09-07-2025 12:40:13</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>09-07-2025 13:25:13</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n">
+        <v>252785</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>09-07-2025 13:52:11</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>09-07-2025 14:17:11</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>251231</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>10-07-2025 07:15:32</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>10-07-2025 08:05:32</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n">
+        <v>251685</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>10-07-2025 13:17:50</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>10-07-2025 14:07:50</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>252547</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>11-07-2025 07:46:36</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>11-07-2025 08:16:36</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>252517</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>10-07-2025 13:19:12</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>10-07-2025 13:51:12</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="n">
-        <v>252245</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>11-07-2025 08:11:15</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>11-07-2025 08:28:15</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="n">
-        <v>252686</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>14-07-2025 08:38:01</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>14-07-2025 08:55:01</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="n">
-        <v>245623</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>14-07-2025 14:24:10</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>14-07-2025 14:41:10</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>252778</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2025 14:17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>252517</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>BIMEC 3</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>17-07-2025 14:00:00</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17-07-2025 14:17:00</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="2" t="n">
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>17-07-2025 14:21:00</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="n">
         <v>7</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>252779</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2025 08:57:59</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2025 09:16:59</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>252576</v>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2025 12:21:16</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2025 12:36:16</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
